--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260617.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260617.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>144,482</t>
+          <t>99,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>144,482</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,893,321</t>
+          <t>1,001,822</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,001,822</t>
+          <t>1,893,321</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>938,659</t>
+          <t>371,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>577,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>577,000</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>371,000</t>
+          <t>938,659</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,575,703</t>
+          <t>7,349,249</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>10,381,121</t>
+          <t>2,575,703</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>7,349,249</t>
+          <t>10,381,121</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2,132,107</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,132,107</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>5,015,956</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>828,000</t>
+          <t>5,015,956</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>828,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>90,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>90,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>1,723,000</t>
+          <t>327,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>1,723,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -2103,6 +2103,24 @@
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>73,921</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
